--- a/templates/整改表模板.xlsx
+++ b/templates/整改表模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="底盘一组" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="底盘二组" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="前悬一组" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="前悬二组" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="底盘一组" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="底盘二组" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前悬一组" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前悬二组" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,33 +443,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17.6" customWidth="1" min="5" max="5"/>
+    <col width="19.8" customWidth="1" min="5" max="5"/>
     <col width="17.6" customWidth="1" min="6" max="6"/>
-    <col width="17.6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19.8" customWidth="1" min="7" max="7"/>
+    <col width="17.6" customWidth="1" min="8" max="8"/>
+    <col width="17.6" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13.2" customWidth="1" min="12" max="12"/>
-    <col width="30.8" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="15.4" customWidth="1" min="17" max="17"/>
-    <col width="15.4" customWidth="1" min="18" max="18"/>
-    <col width="15.4" customWidth="1" min="19" max="19"/>
-    <col width="15.4" customWidth="1" min="20" max="20"/>
-    <col width="19.8" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="13.2" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13.2" customWidth="1" min="14" max="14"/>
+    <col width="13.2" customWidth="1" min="15" max="15"/>
+    <col width="30.8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="15.4" customWidth="1" min="21" max="21"/>
+    <col width="15.4" customWidth="1" min="22" max="22"/>
+    <col width="15.4" customWidth="1" min="23" max="23"/>
+    <col width="15.4" customWidth="1" min="24" max="24"/>
+    <col width="19.8" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="13.2" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -495,100 +499,120 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>T-1日*系统排班</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>T0日*系统排班</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>T+1日*系统排班</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>开始加班打卡时间</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>结束加班打卡时间</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>开始日期</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>结束日期</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>开始时间</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>结束时间</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>转换加班区间</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>上报加班时数</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>实际加班时数(未减吃饭时间)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>差异</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>提醒信息</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>就餐信息</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>处置方式</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>修改后开始日期</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>修改后开始时间</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>修改后结束日期</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>修改后结束时间</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>修改后上报加班时数</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>调班日期</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>调班班次</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>特殊情况说明</t>
         </is>
@@ -615,80 +639,100 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>双班中班 2026-07-31 15:45:00~2026-08-01 00:20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>双班早班 2026-08-01 07:00:00~2026-08-01 15:45:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>固定班 2026-08-02 08:45:00~2026-08-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>2026-08-01 16:56:29</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>15:45-18:45</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>【加班结束卡】请确认加班结束时间</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>修改</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="Y2" t="n">
         <v>3</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -701,33 +745,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17.6" customWidth="1" min="5" max="5"/>
+    <col width="19.8" customWidth="1" min="5" max="5"/>
     <col width="17.6" customWidth="1" min="6" max="6"/>
-    <col width="17.6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19.8" customWidth="1" min="7" max="7"/>
+    <col width="17.6" customWidth="1" min="8" max="8"/>
+    <col width="17.6" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13.2" customWidth="1" min="12" max="12"/>
-    <col width="30.8" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="15.4" customWidth="1" min="17" max="17"/>
-    <col width="15.4" customWidth="1" min="18" max="18"/>
-    <col width="15.4" customWidth="1" min="19" max="19"/>
-    <col width="15.4" customWidth="1" min="20" max="20"/>
-    <col width="19.8" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="13.2" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13.2" customWidth="1" min="14" max="14"/>
+    <col width="13.2" customWidth="1" min="15" max="15"/>
+    <col width="30.8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="15.4" customWidth="1" min="21" max="21"/>
+    <col width="15.4" customWidth="1" min="22" max="22"/>
+    <col width="15.4" customWidth="1" min="23" max="23"/>
+    <col width="15.4" customWidth="1" min="24" max="24"/>
+    <col width="19.8" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="13.2" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -753,100 +801,120 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>T-1日*系统排班</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>T0日*系统排班</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>T+1日*系统排班</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>开始加班打卡时间</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>结束加班打卡时间</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>开始日期</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>结束日期</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>开始时间</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>结束时间</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>转换加班区间</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>上报加班时数</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>实际加班时数(未减吃饭时间)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>差异</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>提醒信息</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>就餐信息</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>处置方式</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>修改后开始日期</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>修改后开始时间</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>修改后结束日期</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>修改后结束时间</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>修改后上报加班时数</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>调班日期</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>调班班次</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>特殊情况说明</t>
         </is>
@@ -873,80 +941,100 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>双班中班 2026-07-31 15:45:00~2026-08-01 00:20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>双班早班 2026-08-01 07:00:00~2026-08-01 15:45:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>固定班 2026-08-02 08:45:00~2026-08-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>2026-08-01 16:56:29</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>15:45-18:45</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>【加班结束卡】请确认加班结束时间</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>修改</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="Y2" t="n">
         <v>3</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -959,33 +1047,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17.6" customWidth="1" min="5" max="5"/>
+    <col width="19.8" customWidth="1" min="5" max="5"/>
     <col width="17.6" customWidth="1" min="6" max="6"/>
-    <col width="17.6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19.8" customWidth="1" min="7" max="7"/>
+    <col width="17.6" customWidth="1" min="8" max="8"/>
+    <col width="17.6" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13.2" customWidth="1" min="12" max="12"/>
-    <col width="30.8" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="15.4" customWidth="1" min="17" max="17"/>
-    <col width="15.4" customWidth="1" min="18" max="18"/>
-    <col width="15.4" customWidth="1" min="19" max="19"/>
-    <col width="15.4" customWidth="1" min="20" max="20"/>
-    <col width="19.8" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="13.2" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13.2" customWidth="1" min="14" max="14"/>
+    <col width="13.2" customWidth="1" min="15" max="15"/>
+    <col width="30.8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="15.4" customWidth="1" min="21" max="21"/>
+    <col width="15.4" customWidth="1" min="22" max="22"/>
+    <col width="15.4" customWidth="1" min="23" max="23"/>
+    <col width="15.4" customWidth="1" min="24" max="24"/>
+    <col width="19.8" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="13.2" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1011,100 +1103,120 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>T-1日*系统排班</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>T0日*系统排班</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>T+1日*系统排班</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>开始加班打卡时间</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>结束加班打卡时间</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>开始日期</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>结束日期</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>开始时间</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>结束时间</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>转换加班区间</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>上报加班时数</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>实际加班时数(未减吃饭时间)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>差异</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>提醒信息</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>就餐信息</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>处置方式</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>修改后开始日期</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>修改后开始时间</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>修改后结束日期</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>修改后结束时间</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>修改后上报加班时数</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>调班日期</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>调班班次</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>特殊情况说明</t>
         </is>
@@ -1131,80 +1243,100 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>双班中班 2026-07-31 15:45:00~2026-08-01 00:20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>双班早班 2026-08-01 07:00:00~2026-08-01 15:45:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>固定班 2026-08-02 08:45:00~2026-08-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>2026-08-01 16:56:29</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>15:45-18:45</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>【加班结束卡】请确认加班结束时间</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>修改</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="Y2" t="n">
         <v>3</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1217,33 +1349,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17.6" customWidth="1" min="5" max="5"/>
+    <col width="19.8" customWidth="1" min="5" max="5"/>
     <col width="17.6" customWidth="1" min="6" max="6"/>
-    <col width="17.6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19.8" customWidth="1" min="7" max="7"/>
+    <col width="17.6" customWidth="1" min="8" max="8"/>
+    <col width="17.6" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13.2" customWidth="1" min="12" max="12"/>
-    <col width="30.8" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="15.4" customWidth="1" min="17" max="17"/>
-    <col width="15.4" customWidth="1" min="18" max="18"/>
-    <col width="15.4" customWidth="1" min="19" max="19"/>
-    <col width="15.4" customWidth="1" min="20" max="20"/>
-    <col width="19.8" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="13.2" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13.2" customWidth="1" min="14" max="14"/>
+    <col width="13.2" customWidth="1" min="15" max="15"/>
+    <col width="30.8" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="15.4" customWidth="1" min="21" max="21"/>
+    <col width="15.4" customWidth="1" min="22" max="22"/>
+    <col width="15.4" customWidth="1" min="23" max="23"/>
+    <col width="15.4" customWidth="1" min="24" max="24"/>
+    <col width="19.8" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="13.2" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1269,100 +1405,120 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>T-1日*系统排班</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>T0日*系统排班</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>T+1日*系统排班</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>开始加班打卡时间</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>结束加班打卡时间</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>开始日期</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>结束日期</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>开始时间</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>结束时间</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>转换加班区间</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>上报加班时数</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>实际加班时数(未减吃饭时间)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>差异</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>提醒信息</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>就餐信息</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>处置方式</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>修改后开始日期</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>修改后开始时间</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>修改后结束日期</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>修改后结束时间</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>修改后上报加班时数</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>调班日期</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>调班班次</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>特殊情况说明</t>
         </is>
@@ -1389,80 +1545,100 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>双班中班 2026-07-31 15:45:00~2026-08-01 00:20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>双班早班 2026-08-01 07:00:00~2026-08-01 15:45:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>固定班 2026-08-02 08:45:00~2026-08-02 17:30:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>2026-08-01 16:56:29</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>15:45</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>18:45</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>15:45-18:45</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>【加班结束卡】请确认加班结束时间</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>修改</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>20260801</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="Y2" t="n">
         <v>3</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/整改表模板.xlsx
+++ b/templates/整改表模板.xlsx
@@ -473,7 +473,7 @@
     <col width="19.8" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="13.2" customWidth="1" min="28" max="28"/>
+    <col width="17.6" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -614,7 +614,7 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>特殊情况说明</t>
+          <t>异常说明（必填）</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <col width="19.8" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="13.2" customWidth="1" min="28" max="28"/>
+    <col width="17.6" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -916,7 +916,7 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>特殊情况说明</t>
+          <t>异常说明（必填）</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
     <col width="19.8" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="13.2" customWidth="1" min="28" max="28"/>
+    <col width="17.6" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>特殊情况说明</t>
+          <t>异常说明（必填）</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
     <col width="19.8" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="13.2" customWidth="1" min="28" max="28"/>
+    <col width="17.6" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>特殊情况说明</t>
+          <t>异常说明（必填）</t>
         </is>
       </c>
     </row>
